--- a/AAII_Financials/Quarterly/RKLB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RKLB_QTR_FIN.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1CFF6A6-9CA9-48C2-8A82-86126E548AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9345"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RKLB" sheetId="6" r:id="rId1"/>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="92">
   <si>
     <t>RKLB</t>
   </si>
@@ -303,7 +304,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
@@ -369,9 +370,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -409,9 +410,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -446,7 +447,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -481,7 +482,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -654,9 +655,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -681,21 +682,20 @@
     <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
@@ -774,14 +774,8 @@
       <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -860,14 +854,8 @@
       <c r="AB8" s="3">
         <v>1400</v>
       </c>
-      <c r="AC8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -946,14 +934,8 @@
       <c r="AB9" s="3">
         <v>5100</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1032,14 +1014,8 @@
       <c r="AB10" s="3">
         <v>-3700</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1068,10 +1044,8 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-      <c r="AC11" s="3"/>
-      <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1150,14 +1124,8 @@
       <c r="AB12" s="3">
         <v>2900</v>
       </c>
-      <c r="AC12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1236,14 +1204,8 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-      <c r="AC13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1322,14 +1284,8 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1408,14 +1364,8 @@
       <c r="AB15" s="3">
         <v>500</v>
       </c>
-      <c r="AC15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1441,10 +1391,8 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-      <c r="AC16" s="3"/>
-      <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1523,14 +1471,8 @@
       <c r="AB17" s="3">
         <v>13600</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1609,14 +1551,8 @@
       <c r="AB18" s="3">
         <v>-12200</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1645,10 +1581,8 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-      <c r="AC19" s="3"/>
-      <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1727,14 +1661,8 @@
       <c r="AB20" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1813,14 +1741,8 @@
       <c r="AB21" s="3">
         <v>-12600</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1899,14 +1821,8 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-      <c r="AC22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1985,14 +1901,8 @@
       <c r="AB23" s="3">
         <v>-14000</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2071,14 +1981,8 @@
       <c r="AB24" s="3">
         <v>300</v>
       </c>
-      <c r="AC24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2157,14 +2061,8 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-      <c r="AC25" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD25" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2243,14 +2141,8 @@
       <c r="AB26" s="3">
         <v>-14200</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2329,14 +2221,8 @@
       <c r="AB27" s="3">
         <v>-14200</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2415,14 +2301,8 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-      <c r="AC28" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD28" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2501,14 +2381,8 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2587,14 +2461,8 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-      <c r="AC30" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD30" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2673,14 +2541,8 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-      <c r="AC31" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD31" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2759,14 +2621,8 @@
       <c r="AB32" s="3">
         <v>1800</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2845,14 +2701,8 @@
       <c r="AB33" s="3">
         <v>-14200</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2931,14 +2781,8 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-      <c r="AC34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD34" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3017,19 +2861,13 @@
       <c r="AB35" s="3">
         <v>-14200</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
@@ -3108,14 +2946,8 @@
       <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3144,10 +2976,8 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-      <c r="AC39" s="3"/>
-      <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3176,10 +3006,8 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-      <c r="AC40" s="3"/>
-      <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3258,14 +3086,8 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3344,14 +3166,8 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-      <c r="AC42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD42" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3430,14 +3246,8 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3516,14 +3326,8 @@
       <c r="AB44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC44" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD44" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3602,14 +3406,8 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3688,14 +3486,8 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3774,14 +3566,8 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3860,14 +3646,8 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3946,14 +3726,8 @@
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4032,14 +3806,8 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-      <c r="AC50" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD50" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4118,14 +3886,8 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-      <c r="AC51" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD51" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4204,14 +3966,8 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4290,14 +4046,8 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-      <c r="AC53" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD53" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -4376,14 +4126,8 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4412,10 +4156,8 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-      <c r="AC55" s="3"/>
-      <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4444,10 +4186,8 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-      <c r="AC56" s="3"/>
-      <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4526,14 +4266,8 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC57" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD57" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4612,14 +4346,8 @@
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4698,14 +4426,8 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4784,14 +4506,8 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4870,14 +4586,8 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4956,14 +4666,8 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD62" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5042,14 +4746,8 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-      <c r="AC63" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD63" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5128,14 +4826,8 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-      <c r="AC64" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD64" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5214,14 +4906,8 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-      <c r="AC65" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD65" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -5300,14 +4986,8 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5336,10 +5016,8 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-      <c r="AC67" s="3"/>
-      <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5418,14 +5096,8 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-      <c r="AC68" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD68" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5504,14 +5176,8 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-      <c r="AC69" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD69" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5590,14 +5256,8 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-      <c r="AC70" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD70" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5676,14 +5336,8 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-      <c r="AC71" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD71" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -5762,14 +5416,8 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5848,14 +5496,8 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-      <c r="AC73" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD73" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5934,14 +5576,8 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-      <c r="AC74" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD74" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6020,14 +5656,8 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-      <c r="AC75" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD75" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -6106,14 +5736,8 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6192,19 +5816,13 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-      <c r="AC77" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD77" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
@@ -6283,14 +5901,8 @@
       <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6369,14 +5981,8 @@
       <c r="AB81" s="3">
         <v>-14200</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6405,10 +6011,8 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-      <c r="AC82" s="3"/>
-      <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6487,14 +6091,8 @@
       <c r="AB83" s="3">
         <v>1300</v>
       </c>
-      <c r="AC83" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6573,14 +6171,8 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-      <c r="AC84" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD84" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6659,14 +6251,8 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-      <c r="AC85" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD85" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6745,14 +6331,8 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-      <c r="AC86" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD86" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6831,14 +6411,8 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-      <c r="AC87" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD87" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6917,14 +6491,8 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-      <c r="AC88" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD88" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7003,14 +6571,8 @@
       <c r="AB89" s="3">
         <v>-7700</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7039,10 +6601,8 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-      <c r="AC90" s="3"/>
-      <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7121,14 +6681,8 @@
       <c r="AB91" s="3">
         <v>-6400</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7207,14 +6761,8 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-      <c r="AC92" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD92" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7293,14 +6841,8 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-      <c r="AC93" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD93" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7379,14 +6921,8 @@
       <c r="AB94" s="3">
         <v>-6400</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7415,10 +6951,8 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-      <c r="AC95" s="3"/>
-      <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7497,14 +7031,8 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7583,14 +7111,8 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-      <c r="AC97" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD97" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7669,14 +7191,8 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-      <c r="AC98" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD98" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7755,14 +7271,8 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-      <c r="AC99" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD99" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7841,14 +7351,8 @@
       <c r="AB100" s="3">
         <v>0</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7927,14 +7431,8 @@
       <c r="AB101" s="3">
         <v>-500</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8012,12 +7510,6 @@
       </c>
       <c r="AB102" s="3">
         <v>-14600</v>
-      </c>
-      <c r="AC102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD102" s="3" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/AAII_Financials/Quarterly/RKLB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RKLB_QTR_FIN.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1CFF6A6-9CA9-48C2-8A82-86126E548AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="RKLB" sheetId="6" r:id="rId1"/>
@@ -23,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
   <si>
     <t>RKLB</t>
   </si>
@@ -304,7 +303,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
@@ -370,9 +369,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -410,9 +409,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -447,7 +446,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -482,7 +481,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -655,367 +654,380 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>234100</v>
+      </c>
+      <c r="E8" s="3">
         <v>200300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>179700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>155100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>144500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>122600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>132400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>104800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>106300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>92800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>60000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>67700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>62000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>54900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>51800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>63100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>55500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>40700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>27500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>11300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>18200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>15700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>10700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>7300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>149500</v>
+      </c>
+      <c r="E9" s="3">
         <v>123900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>111400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>97800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>98100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>87300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>95600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>76800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>79100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>68600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>44500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>52700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>47500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>48500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>49900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>54600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>50500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>37000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>20800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>17700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>8800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>16800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>19800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>12600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>9500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>84600</v>
+      </c>
+      <c r="E10" s="3">
         <v>76500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>68200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>57300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>46400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>35200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>36800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>28000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>27200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>24200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>15500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>15000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>14600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>6400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>8500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>5000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>6700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>-12400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1044,88 +1056,92 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>82400</v>
+      </c>
+      <c r="E12" s="3">
         <v>80500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>78800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>70700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>66100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>55100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>48300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>47700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>39900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>38500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>37500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>26600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>31000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>23900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>14400</v>
-      </c>
-      <c r="R12" s="3">
-        <v>16900</v>
       </c>
       <c r="S12" s="3">
         <v>16900</v>
       </c>
       <c r="T12" s="3">
+        <v>16900</v>
+      </c>
+      <c r="U12" s="3">
         <v>11600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>10600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>13800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>8500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>7000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>7900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>4800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>3100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1204,44 +1220,47 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>10900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-4600</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>-600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-3400</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>1300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-2300</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1254,8 +1273,8 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1284,88 +1303,94 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E15" s="3">
         <v>15000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>14100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>11700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>8800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>8700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>7900</v>
-      </c>
-      <c r="J15" s="3">
-        <v>8100</v>
       </c>
       <c r="K15" s="3">
         <v>8100</v>
       </c>
       <c r="L15" s="3">
+        <v>8100</v>
+      </c>
+      <c r="M15" s="3">
         <v>8300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>7600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>7800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>6800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>7000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>2400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>3400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>2900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>1500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1391,168 +1416,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>291600</v>
+      </c>
+      <c r="E17" s="3">
         <v>245100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>230700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>214000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>204100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>181800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>183900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>156700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>149500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>135800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>107900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>106500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>107200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>100900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>89000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>95100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>88600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>73500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>51800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>57600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>24400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>30500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>34500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>23500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>18500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>13600</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-57500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-44800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-51000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-59000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-59600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-59200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-51500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-51900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-43300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-43100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-47900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-38900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-45200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-46000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-37200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-32000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-33100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-32800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-24300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-52300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-13100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-12300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-18800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-12800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-11200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-12200</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1581,212 +1613,219 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="E20" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
         <v>-200</v>
       </c>
       <c r="G20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H20" s="3">
         <v>1500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1600</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-1000</v>
       </c>
       <c r="R20" s="3">
         <v>-1000</v>
       </c>
       <c r="S20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="T20" s="3">
         <v>-6400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>10500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>21000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-37400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>2400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-29800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-36700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-47000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-52300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-50700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-45300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-42400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-33600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-33700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-42800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-30000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-37600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-37400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-29900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-25100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-31800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-16200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-87100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-13800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-13200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-15300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-10900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-6400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-12600</v>
       </c>
     </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>600</v>
+      </c>
+      <c r="E22" s="3">
         <v>1300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>20900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>600</v>
       </c>
-      <c r="G22" s="3">
-        <v>2400</v>
-      </c>
       <c r="H22" s="3">
+        <v>7400</v>
+      </c>
+      <c r="I22" s="3">
         <v>6800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>24000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>900</v>
-      </c>
-      <c r="M22" s="3">
-        <v>1400</v>
       </c>
       <c r="N22" s="3">
         <v>1400</v>
       </c>
       <c r="O22" s="3">
-        <v>700</v>
+        <v>1400</v>
       </c>
       <c r="P22" s="3">
         <v>700</v>
       </c>
       <c r="Q22" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1821,168 +1860,177 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-43900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-46800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-41600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-59300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-63500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-61400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-51700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-51000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-42500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-44300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-49500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-39200</v>
-      </c>
-      <c r="O23" s="3">
-        <v>-45100</v>
       </c>
       <c r="P23" s="3">
         <v>-45100</v>
       </c>
       <c r="Q23" s="3">
+        <v>-45100</v>
+      </c>
+      <c r="R23" s="3">
         <v>-38200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-32900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-39500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-22300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-89700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-16200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-15600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-18200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-13600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-8700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-14000</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>11300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-41100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-900</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>1000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-1000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-2100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>4400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-6500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-1700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2061,168 +2109,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-49300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-45000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-52900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-18300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-66400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-60600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-52300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-51900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-41600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-44300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-50500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-40600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-45900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-45600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-37200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-34600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-37400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-26700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-88000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-16700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-15900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-18900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-12600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-9200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-14200</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-49300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-45000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-52900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-18300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-66400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-60600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-52300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-51900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-41600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-44300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-50500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-40600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-45900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-45600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-37200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-34600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-37400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-26700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-88000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-16700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-15900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-18900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-12600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-9200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-14200</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2301,8 +2358,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2381,8 +2441,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2461,8 +2524,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2541,168 +2607,177 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-2300</v>
       </c>
       <c r="E32" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
         <v>200</v>
       </c>
       <c r="G32" s="3">
+        <v>200</v>
+      </c>
+      <c r="H32" s="3">
         <v>-1500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1600</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>1000</v>
       </c>
       <c r="R32" s="3">
         <v>1000</v>
       </c>
       <c r="S32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="T32" s="3">
         <v>6400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-10500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-21000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>37400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-49300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-45000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-52900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-18300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-66400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-60600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-52300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-51900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-41600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-44300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-50500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-40600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-45900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-45600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-37200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-34600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-37400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-26700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-88000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-16700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-15900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-18900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-12600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-9200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-14200</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2781,173 +2856,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-49300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-45000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-52900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-18300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-66400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-60600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-52300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-51900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-41600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-44300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-50500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-40600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-45900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-45600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-37200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-34600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-37400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-26700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-88000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-16700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-15900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-18900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-12600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-9200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-14200</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2976,8 +3060,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3006,77 +3091,78 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2129500</v>
+      </c>
+      <c r="E41" s="3">
         <v>1205500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>828700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>807900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>564100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>303100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>271000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>292500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>340900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>365900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>162500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>140900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>197200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>208400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>242500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>333300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>542500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>603100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>691000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>792700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>107900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>34200</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3086,59 +3172,62 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>172700</v>
+      </c>
+      <c r="E42" s="3">
         <v>177900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>187900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>168900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>124100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>125200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>147900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>149900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>155800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>126600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>82300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>147500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>144000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>190400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>229300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>169400</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3151,8 +3240,8 @@
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
+      <c r="X42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y42" s="3">
         <v>0</v>
@@ -3166,77 +3255,80 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>235900</v>
+      </c>
+      <c r="E43" s="3">
         <v>175200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>123000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>120600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>136200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>122500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>111500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>83000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>83100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>59400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>61800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>52200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>52400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>74000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>47500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>71800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>48900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>42500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>16400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>13400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>23200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4600</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3246,77 +3338,80 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>266900</v>
+      </c>
+      <c r="E44" s="3">
         <v>183100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>158400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>145000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>130200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>125600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>119100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>114400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>104500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>99900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>107900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>102400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>102200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>98500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>92300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>86100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>85700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>77900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>47900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>38400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>31500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>25800</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3326,77 +3421,80 @@
       <c r="AB44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E45" s="3">
         <v>9600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>9800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>15800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>9100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5800</v>
-      </c>
-      <c r="L45" s="3">
-        <v>14300</v>
       </c>
       <c r="M45" s="3">
         <v>14300</v>
       </c>
       <c r="N45" s="3">
+        <v>14300</v>
+      </c>
+      <c r="O45" s="3">
         <v>16300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>16700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>17800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>50800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>38800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>29300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>22700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>19500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>10600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>4900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>8100</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3406,77 +3504,80 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2895800</v>
+      </c>
+      <c r="E46" s="3">
         <v>1800400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1365500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1316400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1006100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>724900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>692600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>695500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>751800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>725600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>476700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>506200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>560200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>635300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>662300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>699500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>706400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>746200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>774800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>855000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>167600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>72800</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3486,59 +3587,62 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>85400</v>
+      </c>
+      <c r="E47" s="3">
         <v>93500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>82200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>46200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>61200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>83900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>60700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>61300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>46400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>68600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>79200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>82000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>73900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>47900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>9200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>9800</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3551,8 +3655,8 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X47" s="3">
-        <v>0</v>
+      <c r="X47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y47" s="3">
         <v>0</v>
@@ -3566,77 +3670,80 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>520000</v>
+      </c>
+      <c r="E48" s="3">
         <v>448700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>423700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>382900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>334600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>280400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>262900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>239500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>225800</v>
-      </c>
-      <c r="L48" s="3">
-        <v>219800</v>
       </c>
       <c r="M48" s="3">
         <v>219800</v>
       </c>
       <c r="N48" s="3">
+        <v>219800</v>
+      </c>
+      <c r="O48" s="3">
         <v>196000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>182900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>146300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>152400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>141500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>144300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>149100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>93800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>80200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>76900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>76200</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3646,77 +3753,80 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>619500</v>
+      </c>
+      <c r="E49" s="3">
         <v>429300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>430500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>449700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>124900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>127200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>129700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>132600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>135300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>137900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>139100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>141400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>144300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>147500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>150700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>142900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>142800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>146400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>100800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>13100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>14000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>14300</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3726,8 +3836,11 @@
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3806,8 +3919,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3886,77 +4002,80 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>42500</v>
+      </c>
+      <c r="E52" s="3">
         <v>32000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>20600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>13600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>9700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>15400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>19900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>10300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>12400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>22800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>21600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>16500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>10400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>14600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>7700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>11200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>15800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>11500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>7000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>7400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>5100</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3966,8 +4085,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4046,77 +4168,80 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4187400</v>
+      </c>
+      <c r="E54" s="3">
         <v>2819900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2324500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2221400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1553200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1255000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1184300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1153000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1188600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1181900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>941200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>950500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>981500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>990900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>989100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1001400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1004800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1057500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>980800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>955400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>265900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>168500</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4126,8 +4251,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4156,8 +4284,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4186,77 +4315,78 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>74500</v>
+      </c>
+      <c r="E57" s="3">
         <v>63100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>72700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>61200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>71000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>70200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>53100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>42400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>26500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>26000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>29300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>25000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>25900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>22900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>12100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>13300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>14200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>15100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4100</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4266,8 +4396,11 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4275,40 +4408,40 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>11100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>17100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>16500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>20500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>18500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>11800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>11300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>11000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>23400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>105100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>104400</v>
-      </c>
-      <c r="P58" s="3">
-        <v>2900</v>
       </c>
       <c r="Q58" s="3">
         <v>2900</v>
@@ -4320,7 +4453,7 @@
         <v>2900</v>
       </c>
       <c r="T58" s="3">
-        <v>2800</v>
+        <v>2900</v>
       </c>
       <c r="U58" s="3">
         <v>2800</v>
@@ -4328,8 +4461,8 @@
       <c r="V58" s="3">
         <v>2800</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
+      <c r="W58" s="3">
+        <v>2800</v>
       </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
@@ -4346,77 +4479,80 @@
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>380400</v>
+      </c>
+      <c r="E59" s="3">
         <v>265000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>205500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>236000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>241900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>223300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>227700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>187600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>202800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>172400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>148800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>152700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>155100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>150500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>148000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>145200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>127100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>155400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>90000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>71700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>48200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>35400</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4426,77 +4562,80 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>528200</v>
+      </c>
+      <c r="E60" s="3">
         <v>402300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>334500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>414500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>376500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>348100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>339500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>269200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>266400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>232500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>223400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>303800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>305900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>197300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>162900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>161300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>144100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>173400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>96300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>76700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>51900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>39500</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4506,74 +4645,77 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>133700</v>
+      </c>
+      <c r="E61" s="3">
         <v>138700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>254000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>499500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>481600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>469200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>456400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>458700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>462400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>465800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>158900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>57000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>58600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>150100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>115600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>115000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>114400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>113800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>97300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>96600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>98800</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4586,77 +4728,80 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>23200</v>
+      </c>
+      <c r="E62" s="3">
         <v>13200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>13000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>23400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>37400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>34200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>32800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>37700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>88800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>107900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>35300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>34200</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4666,8 +4811,11 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4746,8 +4894,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4826,8 +4977,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4906,77 +5060,80 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>695200</v>
+      </c>
+      <c r="E66" s="3">
         <v>555600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>602600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>940400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>864700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>823700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>801900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>733200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>733400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>703000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>386700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>364700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>370400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>350900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>315900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>310500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>291300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>324900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>282400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>281300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>186000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>73700</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4986,8 +5143,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5016,8 +5176,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5096,8 +5257,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5176,8 +5340,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5239,13 +5406,13 @@
         <v>0</v>
       </c>
       <c r="W70" s="3">
-        <v>275000</v>
+        <v>0</v>
       </c>
       <c r="X70" s="3">
         <v>275000</v>
       </c>
       <c r="Y70" s="3">
-        <v>0</v>
+        <v>275000</v>
       </c>
       <c r="Z70" s="3">
         <v>0</v>
@@ -5256,8 +5423,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5336,77 +5506,80 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1106200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1056900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1011900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-959000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-940700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-874300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-813700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-761400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-709400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-667800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-623500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-573000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-532500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-486600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-441000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-403700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-369100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-331700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-305000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-308200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-220200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-203600</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5416,8 +5589,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5496,8 +5672,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5576,8 +5755,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5656,77 +5838,80 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3492100</v>
+      </c>
+      <c r="E76" s="3">
         <v>2264400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1721800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1281000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>688500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>431300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>382500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>419800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>455200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>478900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>554500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>585800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>611000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>640000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>673200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>690800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>713500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>732600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>698400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>674100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-195000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-180200</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5736,8 +5921,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5816,173 +6004,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-49300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-45000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-52900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-18300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-66400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-60600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-52300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-51900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-41600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-44300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-50500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-40600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-45900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-45600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-37200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-34600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-37400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-26700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-88000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-16700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-15900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-18900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-12600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-9200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-14200</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6011,88 +6208,92 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E83" s="3">
         <v>6000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6200</v>
-      </c>
-      <c r="F83" s="3">
-        <v>5100</v>
       </c>
       <c r="G83" s="3">
         <v>5100</v>
       </c>
       <c r="H83" s="3">
+        <v>5100</v>
+      </c>
+      <c r="I83" s="3">
         <v>5200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>8400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>7900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>7600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>6100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>3400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>2600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>2500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>2900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>2700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>2300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6171,8 +6372,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6251,8 +6455,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6331,8 +6538,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6411,8 +6621,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6491,88 +6704,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-84100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-50300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-64500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-23500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-23200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-54200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-30900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-13000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-42200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-25200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-6100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-25400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-18900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-23000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-38300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-26300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-21900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-13300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-21100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-15500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-6300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-9300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-7700</v>
       </c>
     </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6601,88 +6820,92 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-27100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-49700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-45900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-32000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-28700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-21600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-11000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-15300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-19200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-10400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-21000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-10600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-12700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-15000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-8300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-12800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-6200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-14300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-9200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-6400</v>
       </c>
     </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6761,8 +6984,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6841,88 +7067,94 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-48900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-35700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-104100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-207200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-28600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-17900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-17300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-10800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-52300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>61200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-32000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-6200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-73200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-188700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-12300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-71800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-80700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-7300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-21400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-6400</v>
       </c>
     </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6951,8 +7183,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6995,8 +7228,8 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -7031,8 +7264,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7111,8 +7347,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7191,8 +7430,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7271,244 +7513,256 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1060100</v>
+      </c>
+      <c r="E100" s="3">
         <v>463300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>189500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>475700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>290500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>115500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>258700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-15000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>14400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>704400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>97000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>20500</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>900</v>
+      </c>
+      <c r="E101" s="3">
         <v>300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>500</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>-600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>4400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>4400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>2700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-500</v>
-      </c>
-      <c r="X101" s="3">
-        <v>500</v>
       </c>
       <c r="Y101" s="3">
         <v>500</v>
       </c>
       <c r="Z101" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA101" s="3">
         <v>-600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>926900</v>
+      </c>
+      <c r="E102" s="3">
         <v>377500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>20800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>243700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>260700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>32900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-21500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-47800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-25200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>203300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>21900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-56300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-10900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-34200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-90400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-210300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-61100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-84300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-101700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>684700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>73700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-18600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-12500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-11700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-4900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-14600</v>
       </c>
     </row>
